--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487432_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487432_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0661</v>
+        <v>1.9388</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0524</v>
+        <v>1.2357</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9863</v>
+        <v>0.7032</v>
       </c>
       <c r="G2" t="n">
-        <v>1.644</v>
+        <v>0.4097</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7489</v>
+        <v>-0.3181</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8951</v>
+        <v>0.7278</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5544</v>
+        <v>0.0608</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8529</v>
+        <v>0.0204</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7015</v>
+        <v>0.0404</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9105</v>
+        <v>0.3489</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.104</v>
+        <v>-0.3385</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1935</v>
+        <v>0.6874</v>
       </c>
       <c r="P2" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-2.9377</v>
-      </c>
       <c r="R2" t="n">
-        <v>2.9377</v>
+        <v>0.1958</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6388</v>
+        <v>-0.2163</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5521</v>
+        <v>-0.0418</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0867</v>
+        <v>-0.1745</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2166</v>
+        <v>1.5495</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8837</v>
+        <v>1.2166</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1003</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7517</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2357</v>
+        <v>2.1908</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5161</v>
+        <v>-1.5744</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4097</v>
+        <v>1.644</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3181</v>
+        <v>0.7489</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7278</v>
+        <v>0.8951</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0608</v>
+        <v>3.5544</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0204</v>
+        <v>2.8529</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0404</v>
+        <v>0.7015</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3489</v>
+        <v>-1.9105</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3385</v>
+        <v>-2.104</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6874</v>
+        <v>0.1935</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1958</v>
+        <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4034</v>
+        <v>0.1891</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0418</v>
+        <v>0.6905</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3616</v>
+        <v>-0.5014</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5495</v>
+        <v>-1.2166</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3329</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5831</v>
+        <v>0.0056</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2194</v>
+        <v>2.1764</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6362</v>
+        <v>-2.1709</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0026</v>
@@ -766,13 +766,13 @@
         <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1317</v>
+        <v>-0.4458</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2294</v>
+        <v>0.1864</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="V4" t="n">
         <v>1.8249</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1051</v>
+        <v>-0.2105</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1424</v>
+        <v>0.5538</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0373</v>
+        <v>-0.7643</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2231</v>
+        <v>1.288</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2334</v>
+        <v>0.2621</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0104</v>
+        <v>1.0259</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.621</v>
+        <v>0.8548</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.621</v>
+        <v>0.1225</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.7323</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6021</v>
+        <v>0.4332</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6125</v>
+        <v>0.1396</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0104</v>
+        <v>0.2937</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1387</v>
+        <v>-0.9282</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1445</v>
+        <v>-0.5764</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0058</v>
+        <v>-0.3518</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6083</v>
+        <v>-1.5495</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0576</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4036</v>
+        <v>-0.5098</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4944</v>
+        <v>-0.654</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8979</v>
+        <v>0.1442</v>
       </c>
       <c r="G6" t="n">
-        <v>1.288</v>
+        <v>-1.2231</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2621</v>
+        <v>-1.2334</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0259</v>
+        <v>0.0104</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8548</v>
+        <v>-0.621</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1225</v>
+        <v>-0.621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7323</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4332</v>
+        <v>-0.6021</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1396</v>
+        <v>-0.6125</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2937</v>
+        <v>0.0104</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1213</v>
+        <v>0.734</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6358</v>
+        <v>0.6328</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4855</v>
+        <v>0.1012</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5495</v>
+        <v>-0.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8249</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2612</v>
+        <v>-0.6158</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0652</v>
+        <v>-1.5535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.804</v>
+        <v>0.9377</v>
       </c>
       <c r="G7" t="n">
         <v>-1.411</v>
@@ -1000,13 +1000,13 @@
         <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1036</v>
+        <v>-0.4583</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1606</v>
+        <v>0.3511</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9431</v>
+        <v>-0.8094</v>
       </c>
       <c r="V7" t="n">
         <v>0.6659</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9411</v>
+        <v>-1.9991</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7628</v>
+        <v>-0.6605</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1783</v>
+        <v>-1.3387</v>
       </c>
       <c r="G8" t="n">
         <v>-2.1336</v>
@@ -1078,13 +1078,13 @@
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>0.113</v>
+        <v>0.055</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1606</v>
+        <v>-0.0582</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2736</v>
+        <v>0.1132</v>
       </c>
       <c r="V8" t="n">
         <v>0.2754</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0275</v>
+        <v>-2.1937</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8069</v>
+        <v>-0.1335</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2206</v>
+        <v>-2.0602</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0596</v>
@@ -1156,13 +1156,13 @@
         <v>2.7419</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4599</v>
+        <v>-0.6261</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4529</v>
+        <v>0.2205</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.007</v>
+        <v>-0.8466</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3329</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>M. ROZAS RAMOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2666</v>
+        <v>-3.69</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8381</v>
+        <v>-3.8628</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4285</v>
+        <v>0.1727</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0262</v>
+        <v>-4.1501</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7136</v>
+        <v>-2.3359</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3126</v>
+        <v>-1.8142</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2407</v>
+        <v>-3.9761</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4428</v>
+        <v>-1.863</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2021</v>
+        <v>-2.1131</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7855</v>
+        <v>-0.174</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2708</v>
+        <v>-0.4729</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5145999999999999</v>
+        <v>0.2988</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.457</v>
+        <v>-0.4017</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3611</v>
+        <v>-0.1241</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8182</v>
+        <v>-0.2776</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6083</v>
+        <v>0.6659</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6083</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ROZAS RAMOS</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5819</v>
+        <v>-4.1864</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4339</v>
+        <v>-2.8381</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.148</v>
+        <v>-1.3483</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1501</v>
+        <v>-2.0262</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3359</v>
+        <v>-1.7136</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8142</v>
+        <v>-0.3126</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.9761</v>
+        <v>-1.2407</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.863</v>
+        <v>-1.4428</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1131</v>
+        <v>0.2021</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.174</v>
+        <v>-0.7855</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4729</v>
+        <v>-0.2708</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2988</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1958</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2935</v>
+        <v>-0.3768</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6952</v>
+        <v>0.3611</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5984</v>
+        <v>-0.738</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6659</v>
+        <v>-0.6083</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5507</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3458</v>
+        <v>-6.3901</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7392</v>
+        <v>-3.9439</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6066</v>
+        <v>-2.4462</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4705</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2963</v>
+        <v>0.252</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4799</v>
+        <v>0.2752</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1836</v>
+        <v>-0.0232</v>
       </c>
       <c r="V12" t="n">
         <v>0.3329</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.5319</v>
+        <v>-17.2346</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.7866</v>
+        <v>-7.4896</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.744999999999999</v>
+        <v>-9.745200000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-10.135</v>
@@ -1438,16 +1438,16 @@
         <v>-10.8949</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7601</v>
+        <v>0.7600999999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>3.479699999999998</v>
+        <v>3.4797</v>
       </c>
       <c r="K13" t="n">
         <v>1.6664</v>
       </c>
       <c r="L13" t="n">
-        <v>1.813099999999999</v>
+        <v>1.8131</v>
       </c>
       <c r="M13" t="n">
         <v>-13.6146</v>
@@ -1468,16 +1468,16 @@
         <v>14.6884</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5202</v>
+        <v>-2.223100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6201</v>
+        <v>1.9171</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.1405</v>
+        <v>-4.140300000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9989000000000003</v>
+        <v>0.9989000000000002</v>
       </c>
       <c r="W13" t="n">
         <v>7.677699999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8634</v>
+        <v>7.374</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0323</v>
+        <v>4.6229</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8311</v>
+        <v>2.7511</v>
       </c>
       <c r="G14" t="n">
         <v>3.6609</v>
@@ -1546,13 +1546,13 @@
         <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.778</v>
+        <v>-0.2673</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3129</v>
+        <v>-0.0965</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0909</v>
+        <v>-0.1708</v>
       </c>
       <c r="V14" t="n">
         <v>1.4344</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7816</v>
+        <v>4.2154</v>
       </c>
       <c r="E15" t="n">
-        <v>4.894</v>
+        <v>2.5663</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1124</v>
+        <v>1.6491</v>
       </c>
       <c r="G15" t="n">
-        <v>1.183</v>
+        <v>3.746</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7332</v>
+        <v>2.9581</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5502</v>
+        <v>0.7879</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4714</v>
+        <v>4.1929</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2289</v>
+        <v>3.5674</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2425</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2884</v>
+        <v>-0.4469</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4957</v>
+        <v>-0.6093</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7927</v>
+        <v>0.1624</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3502</v>
+        <v>2.9377</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7554</v>
+        <v>0.6272</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3212</v>
+        <v>0.2523</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4342</v>
+        <v>0.3749</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3318</v>
+        <v>-0.9412</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7235</v>
+        <v>0.2754</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8845</v>
+        <v>2.8816</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6686</v>
+        <v>3.1543</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2159</v>
+        <v>-0.2728</v>
       </c>
       <c r="G16" t="n">
-        <v>3.746</v>
+        <v>1.183</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9581</v>
+        <v>1.7332</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7879</v>
+        <v>-0.5502</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1929</v>
+        <v>3.4714</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5674</v>
+        <v>3.2289</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.2425</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4469</v>
+        <v>-2.2884</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6093</v>
+        <v>-1.4957</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1624</v>
+        <v>-0.7927</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9377</v>
+        <v>2.3502</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2963</v>
+        <v>1.8553</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3546</v>
+        <v>1.5815</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0583</v>
+        <v>0.2738</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9412</v>
+        <v>-1.3318</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>-0.7235</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4928</v>
+        <v>2.3041</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8323</v>
+        <v>-1.9971</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6604</v>
+        <v>4.3012</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9657</v>
+        <v>-0.3971</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6027</v>
+        <v>1.7353</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.363</v>
+        <v>-2.1324</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6979</v>
+        <v>-1.1709</v>
       </c>
       <c r="K17" t="n">
-        <v>0.415</v>
+        <v>1.3916</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2829</v>
+        <v>-2.5625</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6635</v>
+        <v>0.7738</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0176</v>
+        <v>0.3437</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6459</v>
+        <v>0.4301</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>3.1336</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7718</v>
+        <v>0.2139</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8556</v>
+        <v>-0.4552</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9162</v>
+        <v>0.6692</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8825</v>
+        <v>0.3329</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4332</v>
+        <v>0.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5507</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.032</v>
+        <v>2.0026</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6111</v>
+        <v>0.9105</v>
       </c>
       <c r="F18" t="n">
-        <v>4.6431</v>
+        <v>1.092</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3971</v>
+        <v>2.8229</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7353</v>
+        <v>0.4995</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1324</v>
+        <v>2.3233</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1709</v>
+        <v>2.3385</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3916</v>
+        <v>0.0204</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.5625</v>
+        <v>2.3181</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7738</v>
+        <v>0.4843</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3437</v>
+        <v>0.4791</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4301</v>
+        <v>0.0052</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1543</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1336</v>
+        <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0582</v>
+        <v>0.1601</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0692</v>
+        <v>0.5305</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0111</v>
+        <v>-0.3704</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3329</v>
+        <v>0.3905</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2754</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALVAREZ JORGE</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4743</v>
+        <v>1.9984</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7059</v>
+        <v>1.7066</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7685</v>
+        <v>0.2918</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8229</v>
+        <v>-0.9657</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4995</v>
+        <v>-0.6027</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3233</v>
+        <v>-0.363</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3385</v>
+        <v>0.6979</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0204</v>
+        <v>0.415</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3181</v>
+        <v>0.2829</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4843</v>
+        <v>-1.6635</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4791</v>
+        <v>-1.0176</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0052</v>
+        <v>-0.6459</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3709</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5875</v>
+        <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3681</v>
+        <v>1.2774</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3258</v>
+        <v>0.7299</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6939</v>
+        <v>0.5476</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3905</v>
+        <v>1.8825</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3905</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. NIETO FONTAIÑA</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7553</v>
+        <v>1.4906</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5089</v>
+        <v>1.0866</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2465</v>
+        <v>0.404</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2629</v>
+        <v>3.2684</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6822</v>
+        <v>0.7779</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9451000000000001</v>
+        <v>2.4905</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6774</v>
+        <v>3.2507</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.7758</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6774</v>
+        <v>2.475</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4145</v>
+        <v>0.0177</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6822</v>
+        <v>0.0021</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2677</v>
+        <v>0.0156</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9018</v>
+        <v>-0.1914</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1863</v>
+        <v>-0.2276</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2844</v>
+        <v>0.0362</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2754</v>
+        <v>-0.9988</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6434</v>
+        <v>1.3285</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7795</v>
+        <v>-0.3943</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1362</v>
+        <v>1.7228</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2684</v>
+        <v>0.5546</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7779</v>
+        <v>1.9446</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4905</v>
+        <v>-1.3901</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2507</v>
+        <v>0.9963</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7758</v>
+        <v>1.7353</v>
       </c>
       <c r="L21" t="n">
-        <v>2.475</v>
+        <v>-0.739</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0177</v>
+        <v>-0.4417</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0021</v>
+        <v>0.2094</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0156</v>
+        <v>-0.6511</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1543</v>
+        <v>-2.9377</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5668</v>
+        <v>2.7419</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0386</v>
+        <v>-0.2469</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5346</v>
+        <v>0.3305</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.504</v>
+        <v>-0.5774</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9988</v>
+        <v>1.2166</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2178</v>
+        <v>1.2166</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>S. NIETO FONTAIÑA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0572</v>
+        <v>0.4289</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.213</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1558</v>
+        <v>0.3294</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5546</v>
+        <v>-0.2629</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9446</v>
+        <v>0.6822</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3901</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9963</v>
+        <v>-0.6774</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7353</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.739</v>
+        <v>-0.6774</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4417</v>
+        <v>0.4145</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2094</v>
+        <v>0.6822</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6511</v>
+        <v>-0.2677</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7419</v>
+        <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6325</v>
+        <v>0.5755</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4882</v>
+        <v>0.7769</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1443</v>
+        <v>-0.2014</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2166</v>
+        <v>-0.2754</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5189</v>
+        <v>-0.2506</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3655</v>
+        <v>-0.2631</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1534</v>
+        <v>0.0126</v>
       </c>
       <c r="G23" t="n">
         <v>0.0413</v>
@@ -2248,13 +2248,13 @@
         <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1069</v>
+        <v>0.3752</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0465</v>
+        <v>0.1488</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0605</v>
+        <v>0.2264</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2754</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8196</v>
+        <v>-3.5129</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4869</v>
+        <v>-1.7472</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3326</v>
+        <v>-1.7657</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5165</v>
@@ -2326,13 +2326,13 @@
         <v>1.7626</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4366</v>
+        <v>0.87</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1704</v>
+        <v>0.5693</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2662</v>
+        <v>0.3007</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4332</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>17.5316</v>
+        <v>20.2606</v>
       </c>
       <c r="E25" t="n">
-        <v>9.744999999999999</v>
+        <v>9.745000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>7.7867</v>
+        <v>10.5155</v>
       </c>
       <c r="G25" t="n">
         <v>10.1349</v>
@@ -2374,7 +2374,7 @@
         <v>10.8949</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7602</v>
+        <v>-0.7601999999999995</v>
       </c>
       <c r="J25" t="n">
         <v>13.6144</v>
@@ -2404,13 +2404,13 @@
         <v>20.564</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5202</v>
+        <v>5.249</v>
       </c>
       <c r="T25" t="n">
-        <v>4.1405</v>
+        <v>4.1404</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.62</v>
+        <v>1.1088</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9988999999999999</v>
